--- a/les_octavas.xlsx
+++ b/les_octavas.xlsx
@@ -15,16 +15,15 @@
     <sheet name="RUIDO_ROSA_S1_TERCIO" sheetId="3" state="hidden" r:id="rId1"/>
     <sheet name="RUIDO_ROSA_S2_TERCIO" sheetId="4" state="hidden" r:id="rId2"/>
     <sheet name="SNR_OCT_S1" sheetId="5" r:id="rId3"/>
-    <sheet name="SNR_OCT_S2" sheetId="6" r:id="rId4"/>
-    <sheet name="RUIDO_ROSA_S1_OCT" sheetId="7" state="hidden" r:id="rId5"/>
-    <sheet name="RUIDO_ROSA_S2_OCT" sheetId="8" state="hidden" r:id="rId6"/>
+    <sheet name="RUIDO_ROSA_S1_OCT" sheetId="7" state="hidden" r:id="rId4"/>
+    <sheet name="RUIDO_ROSA_S2_OCT" sheetId="8" state="hidden" r:id="rId5"/>
   </sheets>
   <calcPr calcId="162913"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="140" uniqueCount="40">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="105" uniqueCount="38">
   <si>
     <t>Frequency [Hz]</t>
   </si>
@@ -132,12 +131,6 @@
   </si>
   <si>
     <t>Total Z</t>
-  </si>
-  <si>
-    <t>ROSA</t>
-  </si>
-  <si>
-    <t>fondo_oct_s2</t>
   </si>
   <si>
     <t>snr_oct_s1</t>
@@ -165,24 +158,12 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="2">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="0" tint="-0.14999847407452621"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.79998168889431442"/>
-        <bgColor indexed="64"/>
-      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -197,21 +178,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" quotePrefix="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" quotePrefix="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1043,10 +1015,10 @@
         <v>0</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
     </row>
     <row r="2" spans="1:3">
@@ -1116,7 +1088,7 @@
       </c>
     </row>
     <row r="8" spans="1:3">
-      <c r="A8" s="2" t="s">
+      <c r="A8" s="4" t="s">
         <v>33</v>
       </c>
       <c r="B8" s="2">
@@ -1149,7 +1121,7 @@
       </c>
     </row>
     <row r="15" spans="1:3">
-      <c r="C15" s="7"/>
+      <c r="C15" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -1159,248 +1131,6 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:G23"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.25"/>
-  <cols>
-    <col min="1" max="2" width="11" style="4"/>
-    <col min="3" max="4" width="11" style="6"/>
-    <col min="6" max="6" width="13.25" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:7" s="2" customFormat="1">
-      <c r="A1" s="8" t="s">
-        <v>37</v>
-      </c>
-      <c r="B1" s="8"/>
-      <c r="C1" s="9" t="s">
-        <v>36</v>
-      </c>
-      <c r="D1" s="9"/>
-    </row>
-    <row r="2" spans="1:7">
-      <c r="A2" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B2" s="4" t="s">
-        <v>1</v>
-      </c>
-      <c r="C2" s="5" t="s">
-        <v>0</v>
-      </c>
-      <c r="D2" s="6" t="s">
-        <v>1</v>
-      </c>
-      <c r="F2" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="G2" s="2" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7">
-      <c r="A3" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="B3" s="4">
-        <v>35.5</v>
-      </c>
-      <c r="C3" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="D3" s="6">
-        <v>83.5</v>
-      </c>
-      <c r="F3" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="G3">
-        <f>D3-B3</f>
-        <v>48</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7">
-      <c r="A4" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="B4" s="4">
-        <v>33</v>
-      </c>
-      <c r="C4" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="D4" s="6">
-        <v>78.5</v>
-      </c>
-      <c r="F4" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="G4" s="2">
-        <f t="shared" ref="G4:G11" si="0">D4-B4</f>
-        <v>45.5</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7">
-      <c r="A5" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="B5" s="4">
-        <v>30.3</v>
-      </c>
-      <c r="C5" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="D5" s="6">
-        <v>78.5</v>
-      </c>
-      <c r="F5" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="G5" s="2">
-        <f t="shared" si="0"/>
-        <v>48.2</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7">
-      <c r="A6" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="B6" s="4">
-        <v>27.7</v>
-      </c>
-      <c r="C6" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="D6" s="6">
-        <v>75.7</v>
-      </c>
-      <c r="F6" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="G6" s="2">
-        <f t="shared" si="0"/>
-        <v>48</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7">
-      <c r="A7" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="B7" s="4">
-        <v>18.3</v>
-      </c>
-      <c r="C7" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="D7" s="6">
-        <v>74.400000000000006</v>
-      </c>
-      <c r="F7" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="G7" s="2">
-        <f t="shared" si="0"/>
-        <v>56.100000000000009</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7">
-      <c r="A8" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="B8" s="4">
-        <v>19.2</v>
-      </c>
-      <c r="C8" s="5" t="s">
-        <v>25</v>
-      </c>
-      <c r="D8" s="6">
-        <v>73.599999999999994</v>
-      </c>
-      <c r="F8" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="G8" s="2">
-        <f t="shared" si="0"/>
-        <v>54.399999999999991</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7">
-      <c r="A9" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="B9" s="4">
-        <v>36.6</v>
-      </c>
-      <c r="C9" s="5" t="s">
-        <v>33</v>
-      </c>
-      <c r="D9" s="6">
-        <v>86.3</v>
-      </c>
-      <c r="F9" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="G9" s="2">
-        <f t="shared" si="0"/>
-        <v>49.699999999999996</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7">
-      <c r="A10" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="B10" s="4">
-        <v>59.3</v>
-      </c>
-      <c r="C10" s="5" t="s">
-        <v>34</v>
-      </c>
-      <c r="D10" s="6">
-        <v>91.6</v>
-      </c>
-      <c r="F10" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="G10" s="2">
-        <f t="shared" si="0"/>
-        <v>32.299999999999997</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7">
-      <c r="A11" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="B11" s="4">
-        <v>70.2</v>
-      </c>
-      <c r="C11" s="5" t="s">
-        <v>35</v>
-      </c>
-      <c r="D11" s="6">
-        <v>92</v>
-      </c>
-      <c r="F11" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="G11" s="2">
-        <f t="shared" si="0"/>
-        <v>21.799999999999997</v>
-      </c>
-    </row>
-    <row r="23" spans="7:7">
-      <c r="G23" s="7"/>
-    </row>
-  </sheetData>
-  <mergeCells count="2">
-    <mergeCell ref="A1:B1"/>
-    <mergeCell ref="C1:D1"/>
-  </mergeCells>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:B10"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.25"/>
   <sheetData>
@@ -1490,7 +1220,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:B11"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.25"/>
